--- a/refs/heads/master/CodeSystem-CSTipoCodDiagnostica.xlsx
+++ b/refs/heads/master/CodeSystem-CSTipoCodDiagnostica.xlsx
@@ -147,7 +147,7 @@
     <t>CIE10</t>
   </si>
   <si>
-    <t>Snomed CT</t>
+    <t>SNOMED CT</t>
   </si>
 </sst>
 </file>
